--- a/JsonConverter/ExcelFiles/Upgrade.xlsx
+++ b/JsonConverter/ExcelFiles/Upgrade.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D709AF9C-03F9-41B9-8D5F-D0C7D7FD6E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E4462F-A1EF-4D6F-9E6E-8CEA2B7BC13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="0" windowWidth="31110" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7080" yWindow="780" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -2620,7 +2620,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="3">
-        <v>0.05</v>
+        <v>5</v>
       </c>
       <c r="I4" s="9"/>
     </row>
@@ -2638,10 +2638,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="10">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F5" s="3">
-        <v>0.2</v>
+        <v>12</v>
       </c>
       <c r="I5" s="9"/>
     </row>
@@ -2659,10 +2659,10 @@
         <v>3</v>
       </c>
       <c r="E6" s="10">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="F6" s="3">
-        <v>0.5</v>
+        <v>22</v>
       </c>
       <c r="I6" s="9"/>
     </row>
@@ -2680,10 +2680,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="10">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="F7" s="3">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="I7" s="9"/>
     </row>
@@ -2701,10 +2701,10 @@
         <v>5</v>
       </c>
       <c r="E8" s="10">
-        <v>30000</v>
+        <v>4000</v>
       </c>
       <c r="F8" s="3">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="I8" s="9"/>
     </row>
@@ -2722,10 +2722,10 @@
         <v>6</v>
       </c>
       <c r="E9" s="3">
-        <v>80000</v>
+        <v>12000</v>
       </c>
       <c r="F9" s="3">
-        <v>10</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
@@ -2742,10 +2742,10 @@
         <v>7</v>
       </c>
       <c r="E10" s="3">
-        <v>150000</v>
+        <v>25000</v>
       </c>
       <c r="F10" s="9">
-        <v>25</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1">
@@ -2762,10 +2762,10 @@
         <v>8</v>
       </c>
       <c r="E11" s="3">
-        <v>500000</v>
+        <v>70000</v>
       </c>
       <c r="F11" s="3">
-        <v>50</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1">
@@ -2782,10 +2782,10 @@
         <v>9</v>
       </c>
       <c r="E12" s="3">
-        <v>1000000</v>
+        <v>140000</v>
       </c>
       <c r="F12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1">
@@ -2802,10 +2802,10 @@
         <v>10</v>
       </c>
       <c r="E13" s="3">
-        <v>3000000</v>
+        <v>400000</v>
       </c>
       <c r="F13" s="3">
-        <v>200</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1">
@@ -2842,7 +2842,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="10">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
         <v>0.1</v>
@@ -2862,7 +2862,7 @@
         <v>3</v>
       </c>
       <c r="E16" s="10">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="F16" s="3">
         <v>0.15</v>
@@ -2882,7 +2882,7 @@
         <v>4</v>
       </c>
       <c r="E17" s="10">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="F17" s="3">
         <v>0.2</v>
@@ -2902,7 +2902,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="10">
-        <v>30000</v>
+        <v>4000</v>
       </c>
       <c r="F18" s="3">
         <v>0.25</v>
@@ -2922,7 +2922,7 @@
         <v>6</v>
       </c>
       <c r="E19" s="3">
-        <v>80000</v>
+        <v>12000</v>
       </c>
       <c r="F19" s="3">
         <v>0.3</v>
@@ -2942,7 +2942,7 @@
         <v>7</v>
       </c>
       <c r="E20" s="3">
-        <v>150000</v>
+        <v>25000</v>
       </c>
       <c r="F20" s="3">
         <v>0.35</v>
@@ -2962,7 +2962,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="3">
-        <v>500000</v>
+        <v>70000</v>
       </c>
       <c r="F21" s="3">
         <v>0.4</v>
@@ -2982,7 +2982,7 @@
         <v>9</v>
       </c>
       <c r="E22" s="3">
-        <v>1000000</v>
+        <v>140000</v>
       </c>
       <c r="F22" s="3">
         <v>0.45</v>
@@ -3002,7 +3002,7 @@
         <v>10</v>
       </c>
       <c r="E23" s="3">
-        <v>3000000</v>
+        <v>400000</v>
       </c>
       <c r="F23" s="3">
         <v>0.5</v>
@@ -3025,7 +3025,7 @@
         <v>100</v>
       </c>
       <c r="F24" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1">
@@ -3042,10 +3042,10 @@
         <v>2</v>
       </c>
       <c r="E25" s="10">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F25" s="3">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1">
@@ -3062,10 +3062,10 @@
         <v>3</v>
       </c>
       <c r="E26" s="10">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="F26" s="3">
-        <v>300</v>
+        <v>260</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1">
@@ -3082,10 +3082,10 @@
         <v>4</v>
       </c>
       <c r="E27" s="10">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="F27" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1">
@@ -3102,10 +3102,10 @@
         <v>5</v>
       </c>
       <c r="E28" s="10">
-        <v>30000</v>
+        <v>4000</v>
       </c>
       <c r="F28" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1">
@@ -3122,10 +3122,10 @@
         <v>6</v>
       </c>
       <c r="E29" s="3">
-        <v>80000</v>
+        <v>12000</v>
       </c>
       <c r="F29" s="3">
-        <v>1200</v>
+        <v>850</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1">
@@ -3142,10 +3142,10 @@
         <v>7</v>
       </c>
       <c r="E30" s="3">
-        <v>150000</v>
+        <v>25000</v>
       </c>
       <c r="F30" s="3">
-        <v>1800</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1">
@@ -3162,10 +3162,10 @@
         <v>8</v>
       </c>
       <c r="E31" s="3">
-        <v>500000</v>
+        <v>70000</v>
       </c>
       <c r="F31" s="3">
-        <v>2500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1">
@@ -3182,10 +3182,10 @@
         <v>9</v>
       </c>
       <c r="E32" s="3">
-        <v>1000000</v>
+        <v>140000</v>
       </c>
       <c r="F32" s="3">
-        <v>3500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" customHeight="1">
@@ -3202,10 +3202,10 @@
         <v>10</v>
       </c>
       <c r="E33" s="3">
-        <v>3000000</v>
+        <v>400000</v>
       </c>
       <c r="F33" s="3">
-        <v>5000</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" customHeight="1">
@@ -3225,7 +3225,7 @@
         <v>100</v>
       </c>
       <c r="F34" s="3">
-        <v>0.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1">
@@ -3242,10 +3242,10 @@
         <v>2</v>
       </c>
       <c r="E35" s="10">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F35" s="3">
-        <v>0.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1">
@@ -3262,10 +3262,10 @@
         <v>3</v>
       </c>
       <c r="E36" s="10">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="F36" s="3">
-        <v>0.15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1">
@@ -3282,10 +3282,10 @@
         <v>4</v>
       </c>
       <c r="E37" s="10">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="F37" s="3">
-        <v>0.2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1">
@@ -3302,10 +3302,10 @@
         <v>5</v>
       </c>
       <c r="E38" s="10">
-        <v>30000</v>
+        <v>4000</v>
       </c>
       <c r="F38" s="3">
-        <v>0.25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1">
@@ -3322,10 +3322,10 @@
         <v>6</v>
       </c>
       <c r="E39" s="3">
-        <v>80000</v>
+        <v>12000</v>
       </c>
       <c r="F39" s="3">
-        <v>0.3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" customHeight="1">
@@ -3342,10 +3342,10 @@
         <v>7</v>
       </c>
       <c r="E40" s="3">
-        <v>150000</v>
+        <v>25000</v>
       </c>
       <c r="F40" s="3">
-        <v>0.38</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" customHeight="1">
@@ -3362,10 +3362,10 @@
         <v>8</v>
       </c>
       <c r="E41" s="3">
-        <v>500000</v>
+        <v>70000</v>
       </c>
       <c r="F41" s="3">
-        <v>0.46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1">
@@ -3382,10 +3382,10 @@
         <v>9</v>
       </c>
       <c r="E42" s="3">
-        <v>1000000</v>
+        <v>140000</v>
       </c>
       <c r="F42" s="3">
-        <v>0.54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" customHeight="1">
@@ -3402,10 +3402,10 @@
         <v>10</v>
       </c>
       <c r="E43" s="3">
-        <v>3000000</v>
+        <v>400000</v>
       </c>
       <c r="F43" s="3">
-        <v>0.6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Upgrade.xlsx
+++ b/JsonConverter/ExcelFiles/Upgrade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E4462F-A1EF-4D6F-9E6E-8CEA2B7BC13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BC8459-4D56-4770-8032-3987F1DF4806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7080" yWindow="780" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3025,7 +3025,7 @@
         <v>100</v>
       </c>
       <c r="F24" s="3">
-        <v>80</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1">
@@ -3045,7 +3045,7 @@
         <v>300</v>
       </c>
       <c r="F25" s="3">
-        <v>160</v>
+        <v>700</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1">
@@ -3065,7 +3065,7 @@
         <v>500</v>
       </c>
       <c r="F26" s="3">
-        <v>260</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1">
@@ -3085,7 +3085,7 @@
         <v>1000</v>
       </c>
       <c r="F27" s="3">
-        <v>400</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1">
@@ -3105,7 +3105,7 @@
         <v>4000</v>
       </c>
       <c r="F28" s="3">
-        <v>600</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1">
@@ -3125,7 +3125,7 @@
         <v>12000</v>
       </c>
       <c r="F29" s="3">
-        <v>850</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1">
@@ -3145,7 +3145,7 @@
         <v>25000</v>
       </c>
       <c r="F30" s="3">
-        <v>1150</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1">
@@ -3165,7 +3165,7 @@
         <v>70000</v>
       </c>
       <c r="F31" s="3">
-        <v>1500</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1">
@@ -3185,7 +3185,7 @@
         <v>140000</v>
       </c>
       <c r="F32" s="3">
-        <v>2000</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" customHeight="1">
@@ -3205,7 +3205,7 @@
         <v>400000</v>
       </c>
       <c r="F33" s="3">
-        <v>2700</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" customHeight="1">
@@ -3225,7 +3225,7 @@
         <v>100</v>
       </c>
       <c r="F34" s="3">
-        <v>2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1">
@@ -3245,7 +3245,7 @@
         <v>300</v>
       </c>
       <c r="F35" s="3">
-        <v>5</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1">
@@ -3265,7 +3265,7 @@
         <v>500</v>
       </c>
       <c r="F36" s="3">
-        <v>9</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1">
@@ -3285,7 +3285,7 @@
         <v>1000</v>
       </c>
       <c r="F37" s="3">
-        <v>14</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1">
@@ -3305,7 +3305,7 @@
         <v>4000</v>
       </c>
       <c r="F38" s="3">
-        <v>20</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1">
@@ -3325,7 +3325,7 @@
         <v>12000</v>
       </c>
       <c r="F39" s="3">
-        <v>28</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" customHeight="1">
@@ -3345,7 +3345,7 @@
         <v>25000</v>
       </c>
       <c r="F40" s="3">
-        <v>38</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" customHeight="1">
@@ -3365,7 +3365,7 @@
         <v>70000</v>
       </c>
       <c r="F41" s="3">
-        <v>50</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1">
@@ -3385,7 +3385,7 @@
         <v>140000</v>
       </c>
       <c r="F42" s="3">
-        <v>65</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" customHeight="1">
@@ -3405,7 +3405,7 @@
         <v>400000</v>
       </c>
       <c r="F43" s="3">
-        <v>85</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Upgrade.xlsx
+++ b/JsonConverter/ExcelFiles/Upgrade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BC8459-4D56-4770-8032-3987F1DF4806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9A5B67-B76C-4267-90DB-B005E0B323CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7080" yWindow="780" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="720" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -2620,7 +2620,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I4" s="9"/>
     </row>
@@ -2641,7 +2641,7 @@
         <v>300</v>
       </c>
       <c r="F5" s="3">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="I5" s="9"/>
     </row>
@@ -2662,7 +2662,7 @@
         <v>500</v>
       </c>
       <c r="F6" s="3">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="I6" s="9"/>
     </row>
@@ -2683,7 +2683,7 @@
         <v>1000</v>
       </c>
       <c r="F7" s="3">
-        <v>35</v>
+        <v>230</v>
       </c>
       <c r="I7" s="9"/>
     </row>
@@ -2704,7 +2704,7 @@
         <v>4000</v>
       </c>
       <c r="F8" s="3">
-        <v>55</v>
+        <v>450</v>
       </c>
       <c r="I8" s="9"/>
     </row>
@@ -2724,8 +2724,8 @@
       <c r="E9" s="3">
         <v>12000</v>
       </c>
-      <c r="F9" s="3">
-        <v>80</v>
+      <c r="F9" s="9">
+        <v>500</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
@@ -2744,8 +2744,8 @@
       <c r="E10" s="3">
         <v>25000</v>
       </c>
-      <c r="F10" s="9">
-        <v>110</v>
+      <c r="F10" s="3">
+        <v>800</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1">
@@ -2765,7 +2765,7 @@
         <v>70000</v>
       </c>
       <c r="F11" s="3">
-        <v>150</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1">
@@ -2785,7 +2785,7 @@
         <v>140000</v>
       </c>
       <c r="F12" s="3">
-        <v>200</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1">
@@ -2805,7 +2805,7 @@
         <v>400000</v>
       </c>
       <c r="F13" s="3">
-        <v>260</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1">
@@ -3065,7 +3065,7 @@
         <v>500</v>
       </c>
       <c r="F26" s="3">
-        <v>1100</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1">
@@ -3085,7 +3085,7 @@
         <v>1000</v>
       </c>
       <c r="F27" s="3">
-        <v>1600</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1">
@@ -3105,7 +3105,7 @@
         <v>4000</v>
       </c>
       <c r="F28" s="3">
-        <v>2400</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1">
@@ -3125,7 +3125,7 @@
         <v>12000</v>
       </c>
       <c r="F29" s="3">
-        <v>3500</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1">
@@ -3145,7 +3145,7 @@
         <v>25000</v>
       </c>
       <c r="F30" s="3">
-        <v>4700</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1">
@@ -3165,7 +3165,7 @@
         <v>70000</v>
       </c>
       <c r="F31" s="3">
-        <v>6100</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1">
@@ -3185,7 +3185,7 @@
         <v>140000</v>
       </c>
       <c r="F32" s="3">
-        <v>8100</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" customHeight="1">
@@ -3205,7 +3205,7 @@
         <v>400000</v>
       </c>
       <c r="F33" s="3">
-        <v>11000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Upgrade.xlsx
+++ b/JsonConverter/ExcelFiles/Upgrade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9A5B67-B76C-4267-90DB-B005E0B323CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15AB94EF-6571-480A-A380-F94136708BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="720" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2445" yWindow="1050" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="97">
   <si>
     <t>Name</t>
   </si>
@@ -1820,114 +1820,6 @@
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>방식</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>배율방식</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>누적</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">X </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>최종</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>배율로만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>계산</t>
-    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2570,9 +2462,7 @@
       <c r="F2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="13" t="s">
-        <v>97</v>
-      </c>
+      <c r="G2" s="13"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
@@ -2704,7 +2594,7 @@
         <v>4000</v>
       </c>
       <c r="F8" s="3">
-        <v>450</v>
+        <v>340</v>
       </c>
       <c r="I8" s="9"/>
     </row>
@@ -2845,7 +2735,7 @@
         <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1">
@@ -2865,7 +2755,7 @@
         <v>500</v>
       </c>
       <c r="F16" s="3">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1">
@@ -2885,7 +2775,7 @@
         <v>1000</v>
       </c>
       <c r="F17" s="3">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1">
@@ -2905,7 +2795,7 @@
         <v>4000</v>
       </c>
       <c r="F18" s="3">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1">
@@ -2925,7 +2815,7 @@
         <v>12000</v>
       </c>
       <c r="F19" s="3">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
@@ -2945,7 +2835,7 @@
         <v>25000</v>
       </c>
       <c r="F20" s="3">
-        <v>0.35</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1">
@@ -2965,7 +2855,7 @@
         <v>70000</v>
       </c>
       <c r="F21" s="3">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
@@ -2985,7 +2875,7 @@
         <v>140000</v>
       </c>
       <c r="F22" s="3">
-        <v>0.45</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
@@ -3005,7 +2895,7 @@
         <v>400000</v>
       </c>
       <c r="F23" s="3">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1">
